--- a/output/full_scan/batch_seq6_2026-10-08.xlsx
+++ b/output/full_scan/batch_seq6_2026-10-08.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>79.46498953534406</v>
+        <v>79.46498954188367</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26.30022581206391</v>
+        <v>26.3002258251073</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.294172705056316</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>6.943640669522507</v>
+        <v>6.943640669633746</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>57.76986786949732</v>
+        <v>57.76986786145059</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14.00186328606101</v>
+        <v>14.0018633442272</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2.948459975295852</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2133900465286688</v>
+        <v>0.2133900465064079</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>69.08680420698333</v>
+        <v>69.08680421173534</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>29.203562036525</v>
+        <v>29.20356209877885</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1.04617977215236</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1002.50565617565</v>
+        <v>1002.505656175651</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>462.5</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>61.76356247636259</v>
+        <v>61.76356253115798</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14.85445709860809</v>
+        <v>14.85445712645613</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.899798463853325</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>6.305596096148076</v>
+        <v>6.305596094590224</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>76.14308284389271</v>
+        <v>76.14308286109279</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>34.31829021611308</v>
+        <v>34.31829026227608</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2.593281211817178</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4.209842730117293</v>
+        <v>4.20984272989474</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>996.0708311342833</v>
+        <v>996.0708311342815</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>674</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>74.85405227370977</v>
+        <v>74.85405231427151</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>35.91472926034233</v>
+        <v>35.9147292473659</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.6242723612538802</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>13.64172907630605</v>
+        <v>13.64172907508216</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>944</v>
+        <v>984</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>64</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>73.37984875827863</v>
+        <v>73.37984875248804</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25.61489846740357</v>
+        <v>25.61489844028412</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>6.394199577551736</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.950135784865892</v>
+        <v>1.950135784910396</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6194</v>
+        <v>6233</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>929.6543389638226</v>
+        <v>955.4178220010627</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>32.25</v>
+        <v>25.15</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>75.33749263633703</v>
+        <v>81.46445782471895</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>26.50443259999966</v>
+        <v>37.07336608920084</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.565433896382268</v>
+        <v>1.64178220010628</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2096643150866002</v>
+        <v>0.4529599017441894</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>65.24907073680322</v>
+        <v>65.24907101546721</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19.69315239339188</v>
+        <v>19.69315240545272</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1.344300814691493</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.6834629208336281</v>
+        <v>0.6834629201660084</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6233</v>
+        <v>6187</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>915.4178220010627</v>
+        <v>910.9247498611196</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>25.15</v>
+        <v>1525</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,29 +1029,29 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>81.46445781871221</v>
+        <v>68.89639463551066</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>37.0733660917432</v>
+        <v>25.56806467603485</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.64178220010628</v>
+        <v>1.265613054317315</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.4529599017330638</v>
+        <v>30.39538346955518</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>69.97278566132701</v>
+        <v>69.97278570886206</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>18.45591778370656</v>
+        <v>18.45591780997578</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>4.362155599929602</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>6.897375922556474</v>
+        <v>6.89737592200013</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6257</v>
+        <v>6194</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>889.0200368968415</v>
+        <v>899.6543389638226</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>283</v>
+        <v>32.25</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>72.62807071259762</v>
+        <v>75.33749264635546</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>34.3569085081644</v>
+        <v>26.50443267888965</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.471073908331133</v>
+        <v>1.565433896382268</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>4.2508776400958</v>
+        <v>0.2096643150977287</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6163</v>
+        <v>6257</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>886.2894803235862</v>
+        <v>889.0200368968415</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>43.85</v>
+        <v>283</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>59.88611556736676</v>
+        <v>72.62807070791342</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>16.82826801662734</v>
+        <v>34.35690854750507</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.901939468960706</v>
+        <v>1.471073908331133</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.3115398573959647</v>
+        <v>4.250877640073545</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6187</v>
+        <v>6274</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>870.9247498611184</v>
+        <v>885.7592487529702</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1525</v>
+        <v>1740</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,25 +1241,25 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>68.89639464883851</v>
+        <v>67.59519846659254</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>25.56806471649482</v>
+        <v>24.52050905404415</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.265613054317315</v>
+        <v>0.8230606874435739</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>30.3953834668848</v>
+        <v>36.04697196251469</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6274</v>
+        <v>6163</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>845.7592487529687</v>
+        <v>856.2894803235862</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1740</v>
+        <v>43.85</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,29 +1294,29 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>67.59519845987775</v>
+        <v>59.88611552561413</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>24.52050916655994</v>
+        <v>16.82826803470885</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.8230606874435739</v>
+        <v>1.901939468960706</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>36.04697195739624</v>
+        <v>0.3115398574404739</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>818.8732812276771</v>
+        <v>838.8732812276769</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>49.6</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>64.08057658534406</v>
+        <v>64.0805765719719</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>20.23027680793451</v>
+        <v>20.23027685021475</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.279024845270974</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.0999853221972634</v>
+        <v>0.0999853223530497</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6205</v>
+        <v>6190</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>802.1566046454188</v>
+        <v>838.2033652565141</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>55.43677587089524</v>
+        <v>67.17796667224516</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>32.04125257685523</v>
+        <v>23.15136196679104</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.3205447993659142</v>
+        <v>1.058643954916541</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.2588872810007756</v>
+        <v>0.9227012507353138</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6190</v>
+        <v>6205</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>798.2033652565133</v>
+        <v>802.1566046454188</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>76.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>67.1779666074676</v>
+        <v>55.43677585189899</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.15136197991007</v>
+        <v>32.04125259484862</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.058643954916541</v>
+        <v>0.3205447993659142</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,11 +1471,11 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.9227012505127848</v>
+        <v>0.2588872808783855</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>67.80021507973908</v>
+        <v>67.80021508070274</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>35.84827104008666</v>
+        <v>35.84827103040959</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1.363261771975065</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.9794340000545848</v>
+        <v>0.9794340003327732</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>68.19649828433313</v>
+        <v>68.1964983983091</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>26.39994666101917</v>
+        <v>26.39994667318064</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.7283742089832541</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-1.068668999419352</v>
+        <v>-1.068668999753154</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6285</v>
+        <v>6245</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>776.6359462448638</v>
+        <v>776.9056086942354</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>256.5</v>
+        <v>88</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>64.43952006035042</v>
+        <v>57.55349529316179</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20.54028037169087</v>
+        <v>32.3992546215789</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.7635946244863818</v>
+        <v>0.4282643300109952</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>3.549193878720281</v>
+        <v>0.1197724852938846</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6239</v>
+        <v>6285</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>776.1255125146681</v>
+        <v>776.6359462448638</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>308</v>
+        <v>256.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>61.5401359954919</v>
+        <v>64.43952001476103</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>18.26157804992167</v>
+        <v>20.54028035680201</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.06746148933019</v>
+        <v>0.7635946244863818</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>2.580898404245996</v>
+        <v>3.549193878831565</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6416</v>
+        <v>6239</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>750.1439316319814</v>
+        <v>776.1255125146679</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>120.5</v>
+        <v>308</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>60.81933926458088</v>
+        <v>61.54013601219298</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>34.49426503798122</v>
+        <v>18.26157809998703</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.8989905060510612</v>
+        <v>1.06746148933019</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.3231481376346394</v>
+        <v>2.580898403912211</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6263</v>
+        <v>6204</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>740.5428118815508</v>
+        <v>761.8199070005921</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>176</v>
+        <v>111.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>66.88591422866432</v>
+        <v>64.13753878107569</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>25.4711618301133</v>
+        <v>31.22081947259757</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.654281188155089</v>
+        <v>0.7072389501012587</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>2.300087960830902</v>
+        <v>0.6257119065077337</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6245</v>
+        <v>6416</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>736.9056086942353</v>
+        <v>750.1439316319814</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>88</v>
+        <v>120.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>57.55349527008578</v>
+        <v>60.81933929535338</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>32.39925462719691</v>
+        <v>34.49426503798122</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4282643300109952</v>
+        <v>0.8989905060510612</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.119772485316147</v>
+        <v>-0.3231481378794312</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6438</v>
+        <v>6175</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>726.3653569529291</v>
+        <v>748.9118510935219</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>164.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>64.10458726058948</v>
+        <v>62.60319953987802</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>33.00391608913698</v>
+        <v>21.19958399299881</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5731948857269488</v>
+        <v>1.491185109352189</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>1.102662343240848</v>
+        <v>1.184233753019253</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6204</v>
+        <v>6263</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>721.8199070005912</v>
+        <v>740.5428118815508</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>111.5</v>
+        <v>176</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>64.13753879292</v>
+        <v>66.88591428927262</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>31.22081950124596</v>
+        <v>25.47116182379192</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7072389501012587</v>
+        <v>2.654281188155089</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.6257119065967816</v>
+        <v>2.30008796049709</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6456</v>
+        <v>6438</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>715.5032371557538</v>
+        <v>726.3653569529293</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>100</v>
+        <v>164.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>73.60107203922402</v>
+        <v>64.1045871838121</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>38.96617205740505</v>
+        <v>33.00391610482491</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.050323715575384</v>
+        <v>0.5731948857269488</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>2.589627551823376</v>
+        <v>1.102662344131017</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6225</v>
+        <v>6456</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>711.0273374942136</v>
+        <v>715.5032371557538</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>63.64952482050747</v>
+        <v>73.60107202132252</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>23.43117296182697</v>
+        <v>38.96617212676106</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6748206494924659</v>
+        <v>1.050323715575384</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.7641007324817264</v>
+        <v>2.589627552312971</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6175</v>
+        <v>6259</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>708.9118510935219</v>
+        <v>711.5097406631295</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>77.90000000000001</v>
+        <v>33.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>62.60319966225236</v>
+        <v>65.36613798976518</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>21.19958396040112</v>
+        <v>20.33079371275281</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.491185109352189</v>
+        <v>1.967500366775817</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1.184233752362737</v>
+        <v>0.503035591230281</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6259</v>
+        <v>6225</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>671.5097406631295</v>
+        <v>711.0273374942136</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>33.1</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>65.36613799584993</v>
+        <v>63.64952481305248</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>20.33079369839505</v>
+        <v>23.43117289222213</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.967500366775817</v>
+        <v>0.6748206494924659</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.5030355912414093</v>
+        <v>0.7641007326486333</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6168</v>
+        <v>6227</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>669.6090494912768</v>
+        <v>689.399813925141</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>40.35</v>
+        <v>138.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>55.9804044708346</v>
+        <v>60.6903955107796</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>52.1499382095109</v>
+        <v>43.02121234288609</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7053283181476214</v>
+        <v>0.3196013781485974</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.3481175608069353</v>
+        <v>0.3486736116813951</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2223,21 +2223,21 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6227</v>
+        <v>6168</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>649.399813925141</v>
+        <v>669.6090494912768</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>138.5</v>
+        <v>40.35</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>60.69039548502983</v>
+        <v>55.98040445119885</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>43.02121232773205</v>
+        <v>52.14993814183419</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.3196013781485974</v>
+        <v>0.7053283181476214</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.3486736118816829</v>
+        <v>-0.3481175606845363</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6226</v>
+        <v>6207</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>647.2740664150145</v>
+        <v>660.5053841285638</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>44.4</v>
+        <v>146</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>61.69089634282884</v>
+        <v>64.76383459061591</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>49.45772425759579</v>
+        <v>34.2082555775107</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.9719224449878356</v>
+        <v>0.3660689049433483</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.5618640143919471</v>
+        <v>2.391347895237356</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2329,21 +2329,21 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6442</v>
+        <v>6226</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>643.8982457148593</v>
+        <v>647.2740664150145</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1785</v>
+        <v>44.4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>61.46122240739002</v>
+        <v>61.69089634572368</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>19.96090396113225</v>
+        <v>49.45772430235029</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.60955027857943</v>
+        <v>0.9719224449878356</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>25.75823222078097</v>
+        <v>-0.5618640143941773</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6189</v>
+        <v>6419</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>627.7461519627847</v>
+        <v>646.3376050161758</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>49.3</v>
+        <v>158.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>55.20855819885961</v>
+        <v>52.71695150247466</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>22.76966618963421</v>
+        <v>20.013255353472</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3847961847088648</v>
+        <v>1.402185711225031</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1091770833008444</v>
+        <v>1.186821073077724</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6207</v>
+        <v>6442</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>620.5053841285638</v>
+        <v>643.8982457148588</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>146</v>
+        <v>1785</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>64.76383459020219</v>
+        <v>61.46122239330042</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>34.2082555775107</v>
+        <v>19.96090391438413</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3660689049433483</v>
+        <v>1.60955027857943</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>2.391347895159472</v>
+        <v>25.75823223680413</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6414</v>
+        <v>6292</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>615.9127176217075</v>
+        <v>642.4657636830364</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>399</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,49 +2513,49 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.3092513649184</v>
+        <v>52.38817048253696</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>18.41900790885199</v>
+        <v>35.0887059228752</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.8109504080699972</v>
+        <v>0.73081792615375</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>3.678470893962014</v>
+        <v>-0.0593069296777939</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6419</v>
+        <v>6266</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>606.3376050161758</v>
+        <v>641.5584324230762</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>158.5</v>
+        <v>26.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>52.71695146946448</v>
+        <v>68.06947570820074</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20.01325512426943</v>
+        <v>18.25948553084111</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.402185711225031</v>
+        <v>0.4558432423076169</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.186821074257211</v>
+        <v>0.1854615388077896</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6292</v>
+        <v>6189</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>602.4657636830364</v>
+        <v>627.7461519627847</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>49.3</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>52.38817044815668</v>
+        <v>55.20855805694176</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>35.08870593167891</v>
+        <v>22.76966617056219</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.73081792615375</v>
+        <v>0.3847961847088648</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.0593069296666579</v>
+        <v>0.1091770830115376</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6266</v>
+        <v>6218</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>601.5584324230762</v>
+        <v>624.6135616013803</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>26.5</v>
+        <v>56</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>68.06947575884857</v>
+        <v>52.30982307928421</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.25948551451277</v>
+        <v>43.59201869689436</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.4558432423076169</v>
+        <v>1.057899367362755</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.185461538785535</v>
+        <v>-0.9911700939335608</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6216</v>
+        <v>6414</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>600.4442999291756</v>
+        <v>615.9127176217075</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>20.65</v>
+        <v>399</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,66 +2725,66 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>55.6374270587898</v>
+        <v>54.30925141236648</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>35.45056270346955</v>
+        <v>18.41900796797728</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.884320724978657</v>
+        <v>0.8109504080699972</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2191252318665644</v>
+        <v>3.678470891736591</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6218</v>
+        <v>6173</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>584.6135616013803</v>
+        <v>615.0404335329927</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>56</v>
+        <v>284</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G44" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>52.3098230761304</v>
+        <v>51.81417153388654</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>43.59201869689436</v>
+        <v>38.46113765395066</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.057899367362755</v>
+        <v>0.2894454963500344</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.9911700939892044</v>
+        <v>-4.75790448925655</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2806,38 +2806,38 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6173</v>
+        <v>6216</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>575.0404335329927</v>
+        <v>600.4442999291756</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>284</v>
+        <v>20.65</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>51.81417153322085</v>
+        <v>55.63742710638107</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>38.46113768261758</v>
+        <v>35.45056269081356</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2894454963500344</v>
+        <v>1.884320724978657</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-4.757904489373374</v>
+        <v>0.2191252318443066</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6164</v>
+        <v>6290</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>564.9305972893246</v>
+        <v>587.5331854606771</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>13</v>
+        <v>280.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>58.64477783407896</v>
+        <v>57.48413967295054</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>32.24959470728715</v>
+        <v>32.60549729179129</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5174583600909997</v>
+        <v>0.4592541442673478</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.1385434906090221</v>
+        <v>-0.120355735333824</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6290</v>
+        <v>6182</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>547.5331854606771</v>
+        <v>580.1689465620432</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>280.5</v>
+        <v>129</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>57.48413963410062</v>
+        <v>57.47913295397071</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>32.60549735018608</v>
+        <v>25.99878212565197</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4592541442673478</v>
+        <v>0.8229034555679852</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.1203557348887507</v>
+        <v>1.384159071161655</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6432</v>
+        <v>6164</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>540.3508958877607</v>
+        <v>564.9305972893246</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>66.2</v>
+        <v>13</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>56.5320781823464</v>
+        <v>58.64477782510787</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25.56686266508199</v>
+        <v>32.24959475455059</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6293160744192784</v>
+        <v>0.5174583600909997</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1.146203546154504</v>
+        <v>0.1385434906201499</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6182</v>
+        <v>6166</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>540.1689465620432</v>
+        <v>530.4818744926562</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>57.47913295290286</v>
+        <v>50.29496227308474</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>25.99878213855561</v>
+        <v>26.60156292041889</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.8229034555679852</v>
+        <v>0.8015324316162563</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>1.384159071161655</v>
+        <v>0.7327123175847614</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6166</v>
+        <v>6224</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>530.4818744926561</v>
+        <v>527.4746805181383</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>125</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>50.29496223174268</v>
+        <v>48.91182294386238</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>26.60156291402869</v>
+        <v>29.91343594332426</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8015324316162563</v>
+        <v>0.3820741227775743</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.7327123176070229</v>
+        <v>-1.183048540124158</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6224</v>
+        <v>6426</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>527.4746805181383</v>
+        <v>521.4013294998472</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>79.90000000000001</v>
+        <v>341</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.91182293954376</v>
+        <v>54.67810206496629</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>29.91343590510986</v>
+        <v>37.75453483422483</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3820741227775743</v>
+        <v>0.7857190156112829</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-1.183048540179791</v>
+        <v>-6.176283630135124</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3177,21 +3177,21 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6426</v>
+        <v>6275</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>521.4013294998472</v>
+        <v>516.5883306583498</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>341</v>
+        <v>46.85</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>54.67810206725031</v>
+        <v>54.92194317442267</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>37.75453480232724</v>
+        <v>35.1029317777166</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7857190156112829</v>
+        <v>0.9567766258121844</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-6.176283630201901</v>
+        <v>0.0958878190139032</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6446</v>
+        <v>6432</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>496.6894975653069</v>
+        <v>510.3508958877607</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1195</v>
+        <v>66.2</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,49 +3255,49 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45.16478603427936</v>
+        <v>56.53207817580785</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>15.34007681282915</v>
+        <v>25.56686262549697</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6169973544641724</v>
+        <v>0.6293160744192784</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>4.977192497285095</v>
+        <v>1.146203546143385</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6275</v>
+        <v>6446</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>496.5883306583498</v>
+        <v>496.6894975653068</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>46.85</v>
+        <v>1195</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,49 +3308,49 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>54.92194300033088</v>
+        <v>45.1647860360041</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>35.10293176385834</v>
+        <v>15.34007685143156</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9567766258121844</v>
+        <v>0.6169973544641724</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0958878191808088</v>
+        <v>4.977192496395062</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6230</v>
+        <v>6423</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>486.5628000316174</v>
+        <v>490.5561638857645</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>115.5</v>
+        <v>87.7</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>57.79831851633282</v>
+        <v>54.27043194283701</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18.79603342549613</v>
+        <v>25.42311787074285</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.3880258780331017</v>
+        <v>0.5829207772436857</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.484835824543244</v>
+        <v>0.0393786941462823</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6423</v>
+        <v>6230</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>470.5561638857645</v>
+        <v>486.5628000316162</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>87.7</v>
+        <v>115.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>54.27043194936485</v>
+        <v>57.79831896721706</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>25.42311793668296</v>
+        <v>18.79603346803991</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5829207772436857</v>
+        <v>0.3880258780331017</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0393786942798124</v>
+        <v>0.484835822651646</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6472</v>
+        <v>6229</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>468.032815790522</v>
+        <v>473.33627582486</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>421</v>
+        <v>24.1</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,49 +3467,49 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.67736782426776</v>
+        <v>56.67365361416208</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>28.83595844378036</v>
+        <v>19.9889933015307</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6471612400226758</v>
+        <v>0.6706224607875299</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0550277841386119</v>
+        <v>0.0498264658311689</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6202</v>
+        <v>6223</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>460.5752206640399</v>
+        <v>472.9037658122512</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>58.9</v>
+        <v>5575</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,49 +3520,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>50.8735264005826</v>
+        <v>52.04528800116154</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>17.92504449346445</v>
+        <v>11.69305823744509</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.163762772921273</v>
+        <v>0.5728205667649403</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.3501849270438142</v>
+        <v>31.46568161468948</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6229</v>
+        <v>6472</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>433.3362758248573</v>
+        <v>468.0328157905217</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>24.1</v>
+        <v>421</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,49 +3573,49 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>56.6736534796566</v>
+        <v>49.67736785338496</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19.98899326635359</v>
+        <v>28.835958292447</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6706224607875299</v>
+        <v>0.6471612400226758</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0498264658756779</v>
+        <v>-0.0550277861415358</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6223</v>
+        <v>6202</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>432.90376581225</v>
+        <v>460.5752206640402</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>5575</v>
+        <v>58.9</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,29 +3626,29 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.04528799310214</v>
+        <v>50.87352637436982</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11.69305827642144</v>
+        <v>17.92504452498463</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5728205667649403</v>
+        <v>1.163762772921273</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>31.46568161691463</v>
+        <v>0.3501849271105745</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>418.5553670630191</v>
+        <v>458.5553670630191</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>29.7</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.10329476452492</v>
+        <v>50.1032947298192</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21.55546837294377</v>
+        <v>21.55546829569838</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.4259700814411203</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1056811238707745</v>
+        <v>0.1056811239041529</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6451</v>
+        <v>6462</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>417.1322939649819</v>
+        <v>448.5378324189813</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>420.5</v>
+        <v>100.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>47.84522979925102</v>
+        <v>48.32285828637959</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>7.540572312280814</v>
+        <v>20.040948937815</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5769033129826593</v>
+        <v>0.3640116687412575</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.8792172345279159</v>
+        <v>0.1629282914240892</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6228</v>
+        <v>6279</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>416.5852268132571</v>
+        <v>448.4998802396369</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>55.29037480078443</v>
+        <v>51.00808673813849</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>14.52618586894599</v>
+        <v>29.57421617637868</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2.70414668793422</v>
+        <v>0.5778144179360087</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.808794581485599</v>
+        <v>0.8889113862040228</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6462</v>
+        <v>6441</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>408.5378324189811</v>
+        <v>448.3680615550667</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>100.5</v>
+        <v>22.35</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.32285851229334</v>
+        <v>42.38974280327943</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.04094895948675</v>
+        <v>16.7359633916341</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3640116687412575</v>
+        <v>0.1674061600921483</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1629282918691679</v>
+        <v>-0.3328560194458895</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6279</v>
+        <v>6234</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>408.4998802396369</v>
+        <v>439.4613797171348</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>116</v>
+        <v>39.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>51.00808697649353</v>
+        <v>54.70594203827836</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>29.57421618152345</v>
+        <v>24.35656301897063</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5778144179360087</v>
+        <v>2.407765344398479</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.8889113856476627</v>
+        <v>0.2280600990058658</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6441</v>
+        <v>6451</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>408.3680615550667</v>
+        <v>417.1322939649819</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>22.35</v>
+        <v>420.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>42.38974279923757</v>
+        <v>47.84522978981229</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>16.73596333441317</v>
+        <v>7.540572312280814</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.1674061600921483</v>
+        <v>0.5769033129826593</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.3328560194125083</v>
+        <v>0.8792172338603175</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6192</v>
+        <v>6265</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>400.3797373760052</v>
+        <v>416.1905215904977</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>111.5</v>
+        <v>49.2</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>47.8463322948112</v>
+        <v>45.0849308053389</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>27.87336311733708</v>
+        <v>16.63049652299429</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7365897181654893</v>
+        <v>0.4978613986623879</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.3077326706737229</v>
+        <v>0.2562077696609277</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6443</v>
+        <v>6417</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>400.3228159019485</v>
+        <v>407.9725395491897</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>27</v>
+        <v>103.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>50.96708637657789</v>
+        <v>46.61624856703296</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>28.99356778069024</v>
+        <v>32.72428098669584</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3424332478416957</v>
+        <v>1.690507786029236</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.1348399719809085</v>
+        <v>0.604376876693282</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6234</v>
+        <v>6210</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>399.4613797171342</v>
+        <v>407.3349750541629</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>39.5</v>
+        <v>17.85</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>54.70594200781421</v>
+        <v>51.93485825291294</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>24.35656302572212</v>
+        <v>3.521058822162868</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.407765344398479</v>
+        <v>1.140350288776941</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.2280600989947421</v>
+        <v>0.0643474599042566</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6282</v>
+        <v>6192</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>382.0103818425447</v>
+        <v>400.3797373760053</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>43.2</v>
+        <v>111.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45.18083507064105</v>
+        <v>47.84633261046508</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>15.4175706682326</v>
+        <v>27.87336314441082</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.088988554589016</v>
+        <v>0.7365897181654893</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.2400524017138842</v>
+        <v>0.3077326702286176</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6206</v>
+        <v>6443</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>381.0276399149942</v>
+        <v>400.3228159019485</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>133.5</v>
+        <v>27</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>42.30951236232442</v>
+        <v>50.96708635200682</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13.91767571855539</v>
+        <v>28.9935678727525</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7527343987928723</v>
+        <v>0.3424332478416957</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.6734510057092955</v>
+        <v>0.134839972081054</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6265</v>
+        <v>6291</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>376.1905215904977</v>
+        <v>388.03418492826</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>49.2</v>
+        <v>439</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45.08493080268706</v>
+        <v>42.22283952548904</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.63049652072348</v>
+        <v>23.78749696023577</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4978613986623879</v>
+        <v>0.9376283161202454</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.2562077696831786</v>
+        <v>-8.477996267734937</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6417</v>
+        <v>6228</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>367.9725395491898</v>
+        <v>386.5852268132572</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>103.5</v>
+        <v>18</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46.61624862738142</v>
+        <v>55.29037478876737</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>32.72428100566253</v>
+        <v>14.52618586262748</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.690507786029236</v>
+        <v>2.70414668793422</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.6043768764707482</v>
+        <v>0.8087945813965822</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6210</v>
+        <v>6282</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>367.3349750541629</v>
+        <v>382.0103818425441</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>17.85</v>
+        <v>43.2</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.93485825291294</v>
+        <v>45.18083497098547</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3.521058807815693</v>
+        <v>15.417570663253</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.140350288776941</v>
+        <v>1.088988554589016</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0643474599153829</v>
+        <v>0.2400524017806486</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6246</v>
+        <v>6206</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>366.6516490004624</v>
+        <v>381.0276399149942</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>12.55</v>
+        <v>133.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>44.12994888884128</v>
+        <v>42.30951235131371</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>20.05400865528933</v>
+        <v>13.91767579666506</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2.921391987367654</v>
+        <v>0.7527343987928723</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0208119115563802</v>
+        <v>-0.6734510059318398</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6284</v>
+        <v>6246</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>358.4760665744066</v>
+        <v>366.6516490004609</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>12.55</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>52.67415915101938</v>
+        <v>44.12994973743514</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.76882185148276</v>
+        <v>20.05400858504866</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6159773522481475</v>
+        <v>2.921391987367654</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,51 +4492,51 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.5296212086597608</v>
+        <v>-0.0208119116676522</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6167</v>
+        <v>6284</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>353.4744112284326</v>
+        <v>358.4760665744067</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>10.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G77" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>48.77258362001601</v>
+        <v>52.67415913903354</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>14.02569975265882</v>
+        <v>16.76882189620423</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.9922289282288724</v>
+        <v>0.6159773522481475</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,11 +4545,11 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0238215499270617</v>
+        <v>0.5296212085930062</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>349.898004480072</v>
+        <v>349.8980044800721</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>47.9</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>44.78915609447256</v>
+        <v>44.78915607188766</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>14.37777896928909</v>
+        <v>14.37777899772824</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.2960801209436421</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.1373280436630921</v>
+        <v>-0.1373280435295672</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4608,21 +4608,21 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6188</v>
+        <v>6208</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>348.7914421473523</v>
+        <v>348.8791072952455</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>62.5</v>
+        <v>78.3</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>41.61559815260992</v>
+        <v>51.57313431378976</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>24.89577652952696</v>
+        <v>18.10069650631083</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.205240586704962</v>
+        <v>0.8006348097026877</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.3253041992126573</v>
+        <v>0.7544665883053154</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6291</v>
+        <v>6185</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>348.0341849282599</v>
+        <v>346.598643439104</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>439</v>
+        <v>12.3</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>42.22283953728965</v>
+        <v>38.38011919470132</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>23.78749696370797</v>
+        <v>19.31500520721642</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.9376283161202454</v>
+        <v>1.835561939772701</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-8.477996267512381</v>
+        <v>0.0242238456906397</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6208</v>
+        <v>6435</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>328.8791072952455</v>
+        <v>340.1412249555966</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>78.3</v>
+        <v>259.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>51.57313441133908</v>
+        <v>52.60938929429401</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>18.10069647912168</v>
+        <v>16.62940385459855</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.8006348097026877</v>
+        <v>0.4874922537721792</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.7544665879937513</v>
+        <v>2.126052321378357</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6203</v>
+        <v>6236</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>321.317210347153</v>
+        <v>336.1517152167875</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>59.9</v>
+        <v>0</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>46.17215902451868</v>
+        <v>40.74956787591968</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>9.216922887304779</v>
+        <v>15.30262190307135</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.249264594028412</v>
+        <v>0</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.09504237931193631</v>
+        <v>-1.827411258314468</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6236</v>
+        <v>6220</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>316.1517152167875</v>
+        <v>332.6526782084041</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>40.74956784498743</v>
+        <v>47.47659813469829</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.30262192686087</v>
+        <v>15.00981422852612</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0</v>
+        <v>0.8604789287030653</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.827411258091926</v>
+        <v>0.1101373656368981</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6185</v>
+        <v>6418</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>306.598643439104</v>
+        <v>323.5126855444195</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>12.3</v>
+        <v>34.3</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>38.38011901941079</v>
+        <v>49.66622949997304</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>19.31500520721642</v>
+        <v>31.5832025205298</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.835561939772701</v>
+        <v>0.6850230461123523</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,51 +4916,51 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0242238457017676</v>
+        <v>-0.145748121689812</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6222</v>
+        <v>6167</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>305.0364067731132</v>
+        <v>323.4744112284328</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>19.45</v>
+        <v>10.3</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G85" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>51.48874330017389</v>
+        <v>48.77258409237539</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>7.413113509811259</v>
+        <v>14.02569976876042</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.0616895534910118</v>
+        <v>0.9922289282288724</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.283057776398031</v>
+        <v>0.0238215498603316</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6435</v>
+        <v>6465</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>300.1412249555964</v>
+        <v>319.618888093781</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>259.5</v>
+        <v>41.7</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>52.60938928812899</v>
+        <v>41.64580686829242</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.62940388907344</v>
+        <v>9.406252666683258</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4874922537721792</v>
+        <v>1.185098328064244</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>2.126052321712169</v>
+        <v>0.1797636419483321</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6235</v>
+        <v>6188</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>299.9093986416529</v>
+        <v>318.7914421473522</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>36.1</v>
+        <v>62.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>33.25295792912412</v>
+        <v>41.61559882823463</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>16.40203495137578</v>
+        <v>24.89577662866258</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.636353862264569</v>
+        <v>1.205240586704962</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.2409906220245932</v>
+        <v>0.325304199880271</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6176</v>
+        <v>6217</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>294.4640295341512</v>
+        <v>317.339954911232</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>168</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>48.77287731122584</v>
+        <v>46.34067468086418</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.51442670072649</v>
+        <v>13.64863592572729</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4348668324621864</v>
+        <v>0.8816950788172239</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.2541926802028564</v>
+        <v>-0.1069853220640617</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6220</v>
+        <v>6411</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>292.6526782084049</v>
+        <v>307.9582619076037</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>25.5</v>
+        <v>77.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>47.47659804651758</v>
+        <v>44.55516494287926</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.00981422395956</v>
+        <v>7.741277903514341</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.8604789287030653</v>
+        <v>1.061630723977469</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.1101373656257714</v>
+        <v>0.08538081097513921</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6243</v>
+        <v>6474</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>289.6578205472233</v>
+        <v>307.0053506091726</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>38.45</v>
+        <v>35.45</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45.11486976781102</v>
+        <v>41.10006100095028</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.4742204974749</v>
+        <v>14.25526461937799</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.3811414374332916</v>
+        <v>1.523325087508403</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.2262497862102747</v>
+        <v>0.09937463424993841</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6411</v>
+        <v>6235</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>287.9582619076037</v>
+        <v>299.9093986416535</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>77.5</v>
+        <v>36.1</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>44.55516495085676</v>
+        <v>33.25295697484269</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>7.74127788512177</v>
+        <v>16.40203552758541</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.061630723977469</v>
+        <v>1.636353862264569</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0853808109528869</v>
+        <v>-0.2409906207560992</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6184</v>
+        <v>6176</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>286.119575904058</v>
+        <v>294.4640295341512</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>40</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>41.76788309318856</v>
+        <v>48.77287710712907</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>25.95400185394574</v>
+        <v>12.51442681894661</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.2089990252039252</v>
+        <v>0.4348668324621864</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0533109125359934</v>
+        <v>-0.2541926796307566</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6418</v>
+        <v>6203</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>283.5126855444195</v>
+        <v>291.317210347153</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>34.3</v>
+        <v>59.9</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>49.6662295142553</v>
+        <v>46.17215873510872</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>31.58320247819917</v>
+        <v>9.216922855944976</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.6850230461123523</v>
+        <v>1.249264594028412</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1457481223351909</v>
+        <v>0.09504237893361581</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6465</v>
+        <v>6243</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>279.618888093781</v>
+        <v>289.6578205472233</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>41.7</v>
+        <v>38.45</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>41.64580685496149</v>
+        <v>45.11486981408318</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>9.406252656048268</v>
+        <v>14.47422050402955</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.185098328064244</v>
+        <v>0.3811414374332916</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.1797636420436874</v>
+        <v>0.2262497860322402</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6217</v>
+        <v>6184</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>277.3399549112319</v>
+        <v>286.1195759040581</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>168</v>
+        <v>40</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>46.34067468372177</v>
+        <v>41.76788306841641</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>13.64863599062072</v>
+        <v>25.9540047359469</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8816950788172239</v>
+        <v>0.2089990252039252</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.1069853219193973</v>
+        <v>0.0533109120463983</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6272</v>
+        <v>6222</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>274.1807817869297</v>
+        <v>275.0364067731132</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>25.8</v>
+        <v>19.45</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>48.05776727420688</v>
+        <v>51.488743295798</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>20.95541983766777</v>
+        <v>7.413113537644509</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4051523792768494</v>
+        <v>0.0616895534910118</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1147528799369035</v>
+        <v>0.2830577764091596</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6269</v>
+        <v>6272</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>271.0731048411189</v>
+        <v>274.1807817869298</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>63.6</v>
+        <v>25.8</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>45.0740120579521</v>
+        <v>48.05776732579494</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.06075910108761</v>
+        <v>20.95541984737102</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6677909634672433</v>
+        <v>0.4051523792768494</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1392495283930094</v>
+        <v>-0.1147528800481796</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6474</v>
+        <v>6269</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>267.0053506091725</v>
+        <v>271.0731048411189</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>35.45</v>
+        <v>63.6</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>41.10006146313824</v>
+        <v>45.07401217972424</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>14.25526461937799</v>
+        <v>12.06075918347341</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.523325087508403</v>
+        <v>0.6677909634672433</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,11 +5658,11 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0993746338271056</v>
+        <v>-0.1392495284820216</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>260.2683293963358</v>
+        <v>260.2683293963357</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>18.75</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>41.69041993277978</v>
+        <v>41.69041987627492</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>16.73243017663546</v>
+        <v>16.73243016912364</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.4163025262967711</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.06856179205739291</v>
+        <v>0.0685617920240111</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6237</v>
+        <v>6215</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>257.5962448273104</v>
+        <v>255.0471086599354</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>34.65</v>
+        <v>93.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>46.66207258573912</v>
+        <v>36.11295329110976</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>24.80677593304816</v>
+        <v>9.798471226473838</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6476808746442609</v>
+        <v>2.487407043997548</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0082952631904124</v>
+        <v>-0.1935775210738975</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6215</v>
+        <v>6464</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>255.0471086599356</v>
+        <v>243.7472600616101</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>93.3</v>
+        <v>76.3</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>36.11295299424953</v>
+        <v>44.62086216214763</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>9.798471175062682</v>
+        <v>22.76719014609892</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2.487407043997548</v>
+        <v>0.0758739211042115</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.1935775207400923</v>
+        <v>-0.0559903311266337</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6464</v>
+        <v>6244</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>243.7472600616101</v>
+        <v>238.3841345843215</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>76.3</v>
+        <v>22.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>44.62086216214763</v>
+        <v>40.93586023042185</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>22.76719002288612</v>
+        <v>17.03011852028452</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.0758739211042115</v>
+        <v>0.9075224382208136</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0559903311266337</v>
+        <v>-0.0419286807018686</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6161</v>
+        <v>6201</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>捷波</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>242.2360256311489</v>
+        <v>231.0569135764281</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>49</v>
+        <v>44.15</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>46.47012986972926</v>
+        <v>43.2078597571998</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>9.076027364299922</v>
+        <v>26.98343145902366</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.3064093180084713</v>
+        <v>0.5685829799822503</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0370086347469106</v>
+        <v>-0.0166069864173007</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6244</v>
+        <v>6281</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>238.3841345843227</v>
+        <v>230.3960435151252</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>22.3</v>
+        <v>51</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>40.93586033293165</v>
+        <v>47.00197673440443</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>17.03011836104964</v>
+        <v>10.07706021861419</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.9075224382208136</v>
+        <v>1.38745756334259</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0419286808576487</v>
+        <v>-0.0002543061124941</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6201</v>
+        <v>6409</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>231.0569135764281</v>
+        <v>228.8653854294278</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>44.15</v>
+        <v>868</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>43.20785982192375</v>
+        <v>37.84148844451587</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>26.9834314772787</v>
+        <v>13.41429763359527</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5685829799822503</v>
+        <v>0.8474657377354361</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0166069864395514</v>
+        <v>2.889963616940307</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6281</v>
+        <v>6237</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>230.3960435151754</v>
+        <v>227.5962448273092</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>51</v>
+        <v>34.65</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>47.00197669275644</v>
+        <v>46.662072382813</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>10.07706021861419</v>
+        <v>24.80677598090175</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.38745756334259</v>
+        <v>0.6476808746442609</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0002543061124941</v>
+        <v>-0.0082952622779786</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6409</v>
+        <v>6161</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>捷波</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>228.8653854294277</v>
+        <v>212.2360256311488</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>868</v>
+        <v>49</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>37.84148842909367</v>
+        <v>46.47012988963206</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.41429768949056</v>
+        <v>9.076027381227568</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8474657377354361</v>
+        <v>0.3064093180084713</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>2.889963621391182</v>
+        <v>0.0370086347024067</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6276</v>
+        <v>6177</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>211.8198954547234</v>
+        <v>208.4147303012684</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>19</v>
+        <v>45.95</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>50.52613749193591</v>
+        <v>43.44224238305644</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>16.30507324488453</v>
+        <v>12.80225797012829</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.2102735870154775</v>
+        <v>0.354691712174793</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.059577089277063</v>
+        <v>-0.1171555133994031</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6177</v>
+        <v>6412</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>208.4147303012684</v>
+        <v>192.4196536978067</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>45.95</v>
+        <v>73</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>43.44224248525136</v>
+        <v>32.07702986363576</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.80225802506854</v>
+        <v>18.34389015746456</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.354691712174793</v>
+        <v>1.450007571509841</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.1171555135663086</v>
+        <v>0.130055043177476</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6412</v>
+        <v>6261</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>192.4196536978067</v>
+        <v>186.1726128371073</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>73</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>32.07703001333782</v>
+        <v>42.35688527511441</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18.34389015746456</v>
+        <v>10.2330487939857</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.450007571509841</v>
+        <v>0.958165478506654</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.130055043177476</v>
+        <v>0.0012777892768378</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6261</v>
+        <v>6276</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>186.1726128371074</v>
+        <v>181.8198954547241</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>19</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>42.35688532479227</v>
+        <v>50.52613751987526</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10.23304873218655</v>
+        <v>16.30507301775355</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.958165478506654</v>
+        <v>0.2102735870154775</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,11 +6347,11 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0012777892100649</v>
+        <v>0.0595770887652129</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>178.605901010752</v>
+        <v>148.605901010752</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>42.75</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>48.96324122812001</v>
+        <v>48.96324100123464</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.23222105620131</v>
+        <v>19.23222113048167</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.7730287448142529</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0069697374244466</v>
+        <v>0.0069697375357186</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>47.91922578543535</v>
+        <v>47.91922590086912</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>8.780249839185778</v>
+        <v>8.780249822181149</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.963897398420272</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0452194379851239</v>
+        <v>0.0452194382076676</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45.78275576587996</v>
+        <v>45.78275577003692</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>18.70922705623718</v>
+        <v>18.70922704152799</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.5123952563875328</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.2373580357488426</v>
+        <v>-0.2373580357377152</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.70378021852533</v>
+        <v>44.7037802253525</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8.288036237261622</v>
+        <v>8.288036179015641</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.0008963585434173</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.6926433048049749</v>
+        <v>-0.6926433050163903</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq6_2026-10-08.xlsx
+++ b/output/full_scan/batch_seq6_2026-10-08.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>79.46498954188367</v>
+        <v>79.46498951945375</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26.3002258251073</v>
+        <v>26.30022595783974</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.294172705056316</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>6.943640669633746</v>
+        <v>6.943640670234652</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         <v>57.76986786145059</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14.0018633442272</v>
+        <v>14.00186336069156</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2.948459975295852</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2133900465064079</v>
+        <v>0.2133900464583404</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>69.08680421173534</v>
+        <v>69.08680418374368</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>29.20356209877885</v>
+        <v>29.20356208008065</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1.04617977215236</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.9124050477091998</v>
+        <v>0.9124050478293766</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>61.76356253115798</v>
+        <v>61.76356252876057</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14.85445712645613</v>
+        <v>14.85445713839782</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.899798463853325</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>6.305596094590224</v>
+        <v>6.305596094830549</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>76.14308286109279</v>
+        <v>76.14308282655526</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>34.31829026227608</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4.20984272989474</v>
+        <v>4.209842730014904</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>996.0708311342815</v>
+        <v>996.0708311342833</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>674</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>74.85405231427151</v>
+        <v>74.8540523035328</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>35.9147292473659</v>
+        <v>35.91472929688045</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.6242723612538802</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>13.64172907508216</v>
+        <v>13.64172907652414</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>73.37984875248804</v>
+        <v>73.37984875610198</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>25.61489844028412</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.950135784910396</v>
+        <v>1.950135784886359</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>81.46445782471895</v>
+        <v>81.46445777236974</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>37.07336608920084</v>
+        <v>37.07336610448105</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.64178220010628</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4529599017441894</v>
+        <v>0.4529599017802407</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>65.24907101546721</v>
+        <v>65.2490707613064</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19.69315240545272</v>
+        <v>19.69315240784088</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1.344300814691493</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.6834629201660084</v>
+        <v>0.6834629202861819</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>68.89639463551066</v>
+        <v>68.89639465361061</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>25.56806467603485</v>
+        <v>25.56806469165961</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1.265613054317315</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>30.39538346955518</v>
+        <v>30.39538346919463</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>69.97278570886206</v>
+        <v>69.97278569078239</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>18.45591780997578</v>
+        <v>18.45591782790046</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>4.362155599929602</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>6.89737592200013</v>
+        <v>6.897375923322028</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>75.33749264635546</v>
+        <v>75.33749259721402</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>26.50443267888965</v>
+        <v>26.50443270267381</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.565433896382268</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.2096643150977287</v>
+        <v>0.2096643151337769</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>72.62807070791342</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>34.35690854750507</v>
+        <v>34.35690855663209</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.471073908331133</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>4.250877640073545</v>
+        <v>4.250877639953369</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>885.7592487529702</v>
+        <v>885.7592487529703</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1740</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>67.59519846659254</v>
+        <v>67.59519842116066</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>24.52050905404415</v>
+        <v>24.52050901694153</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.8230606874435739</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>36.04697196251469</v>
+        <v>36.04697197008559</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>59.88611552561413</v>
+        <v>59.88611554884109</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>16.82826803470885</v>
+        <v>16.82826798296572</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.901939468960706</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.3115398574404739</v>
+        <v>0.3115398573563533</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>64.0805765719719</v>
+        <v>64.08057648556726</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>20.23027685021475</v>
+        <v>20.23027684660553</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.279024845270974</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.0999853223530497</v>
+        <v>0.0999853224972547</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>838.2033652565141</v>
+        <v>838.2033652565192</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>76.5</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>67.17796667224516</v>
+        <v>67.17796653183512</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>23.15136196679104</v>
+        <v>23.15136200008063</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>1.058643954916541</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.9227012507353138</v>
+        <v>0.9227012515044336</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.43677585189899</v>
+        <v>55.43677589650424</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>32.04125259484862</v>
+        <v>32.04125263799971</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.3205447993659142</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.2588872808783855</v>
+        <v>0.2588872806260247</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>67.80021508070274</v>
+        <v>67.80021503842451</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>35.84827103040959</v>
+        <v>35.84827095327165</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1.363261771975065</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.9794340003327732</v>
+        <v>0.9794340006452172</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>68.1964983983091</v>
+        <v>68.19649827556573</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>26.39994667318064</v>
+        <v>26.39994673087083</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.7283742089832541</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-1.068668999753154</v>
+        <v>-1.068668999512821</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>776.9056086942354</v>
+        <v>776.9056086942352</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>88</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>57.55349529316179</v>
+        <v>57.55349522059731</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>32.3992546215789</v>
+        <v>32.39925462320264</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>0.4282643300109952</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1197724852938846</v>
+        <v>0.11977248541407</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>64.43952001476103</v>
+        <v>64.43951999707458</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>20.54028035680201</v>
+        <v>20.54028037329116</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.7635946244863818</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>3.549193878831565</v>
+        <v>3.549193878230716</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>776.1255125146679</v>
+        <v>776.1255125146681</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>308</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>61.54013601219298</v>
+        <v>61.54013598821194</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>18.26157809998703</v>
+        <v>18.2615780754512</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>1.06746148933019</v>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>64.13753878107569</v>
+        <v>64.13753879383111</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>31.22081947259757</v>
+        <v>31.22081972788407</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0.7072389501012587</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.6257119065077337</v>
+        <v>0.6257119062914382</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>60.81933929535338</v>
+        <v>60.81933930311666</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>34.49426503798122</v>
+        <v>34.49426505452639</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.8989905060510612</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>62.60319953987802</v>
+        <v>62.60319950201166</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>21.19958399299881</v>
+        <v>21.19958398773892</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1.491185109352189</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>1.184233753019253</v>
+        <v>1.184233752899068</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>66.88591428927262</v>
+        <v>66.88591420944987</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25.47116182379192</v>
+        <v>25.47116182928336</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>2.654281188155089</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>2.30008796049709</v>
+        <v>2.300087960857613</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>726.3653569529293</v>
+        <v>726.3653569529291</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>164.5</v>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>64.1045871838121</v>
+        <v>64.10458709152351</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>33.00391610482491</v>
+        <v>33.0039160886967</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.5731948857269488</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>73.60107202132252</v>
+        <v>73.60107203857173</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>38.96617212676106</v>
+        <v>38.96617216672738</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>1.050323715575384</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>2.589627552312971</v>
+        <v>2.589627552385074</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>65.36613798976518</v>
+        <v>65.3661380445343</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.33079371275281</v>
+        <v>20.330793728338</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1.967500366775817</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.503035591230281</v>
+        <v>0.5030355912062466</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>63.64952481305248</v>
+        <v>63.64952478840734</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23.43117289222213</v>
+        <v>23.43117289688426</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.6748206494924659</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.7641007326486333</v>
+        <v>0.7641007326967051</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>60.6903955107796</v>
+        <v>60.69039550604356</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>43.02121234288609</v>
+        <v>43.0212122671155</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.3196013781485974</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.3486736116813951</v>
+        <v>0.3486736117054549</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>55.98040445119885</v>
+        <v>55.98040444462473</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>52.14993814183419</v>
+        <v>52.14993800182121</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.7053283181476214</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.3481175606845363</v>
+        <v>-0.3481175606965543</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>64.76383459061591</v>
+        <v>64.76383463160613</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>34.2082555775107</v>
+        <v>34.20825560185507</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.3660689049433483</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>2.391347895237356</v>
+        <v>2.391347895333508</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>61.69089634572368</v>
+        <v>61.69089634130896</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>49.45772430235029</v>
+        <v>49.45772446632229</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.9719224449878356</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.5618640143941773</v>
+        <v>-0.561864014370137</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>52.71695150247466</v>
+        <v>52.71695156270656</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>20.013255353472</v>
+        <v>20.01325549556053</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>1.402185711225031</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.186821073077724</v>
+        <v>1.186821072356692</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>643.8982457148588</v>
+        <v>643.8982457148592</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1785</v>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>61.46122239330042</v>
+        <v>61.46122231276667</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>19.96090391438413</v>
+        <v>19.9609038693042</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1.60955027857943</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>25.75823223680413</v>
+        <v>25.75823224954256</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>52.38817048253696</v>
+        <v>52.38817044820993</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>35.0887059228752</v>
+        <v>35.0887055714697</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.73081792615375</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.0593069296777939</v>
+        <v>-0.0593069295095383</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>68.06947570820074</v>
+        <v>68.06947568963692</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>18.25948553084111</v>
+        <v>18.25948552114786</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.4558432423076169</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1854615388077896</v>
+        <v>0.185461538783755</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>627.7461519627847</v>
+        <v>627.7461519627835</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>49.3</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>55.20855805694176</v>
+        <v>55.20855832864774</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>22.76966617056219</v>
+        <v>22.76966613917228</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.3847961847088648</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.1091770830115376</v>
+        <v>0.1091770824827835</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>52.30982307928421</v>
+        <v>52.30982307022713</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>43.59201869689436</v>
+        <v>43.59201887965735</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>1.057899367362755</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.9911700939335608</v>
+        <v>-0.9911700938374252</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>54.30925141236648</v>
+        <v>54.30925154084466</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>18.41900796797728</v>
+        <v>18.41900799872784</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.8109504080699972</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>3.678470891736591</v>
+        <v>3.67847089053484</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.81417153388654</v>
+        <v>51.81417152994361</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>38.46113765395066</v>
+        <v>38.46113759337639</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.2894454963500344</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-4.75790448925655</v>
+        <v>-4.757904489102373</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>55.63742710638107</v>
+        <v>55.63742709707654</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>35.45056269081356</v>
+        <v>35.45056275432712</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>1.884320724978657</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.2191252318443066</v>
+        <v>0.2191252318803594</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>57.48413967295054</v>
+        <v>57.48413961307436</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>32.60549729179129</v>
+        <v>32.60549737115372</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.4592541442673478</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.120355735333824</v>
+        <v>-0.1203557348531561</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>57.47913295397071</v>
+        <v>57.4791329512662</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>25.99878212565197</v>
+        <v>25.99878213888796</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.8229034555679852</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.384159071161655</v>
+        <v>1.384159071185698</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>58.64477782510787</v>
+        <v>58.64477781140761</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>32.24959475455059</v>
+        <v>32.24959476416474</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.5174583600909997</v>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>50.29496227308474</v>
+        <v>50.29496219029219</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>26.60156292041889</v>
+        <v>26.60156294589656</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.8015324316162563</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.7327123175847614</v>
+        <v>0.7327123180414186</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.91182294386238</v>
+        <v>48.91182300432327</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>29.91343594332426</v>
+        <v>29.91343593099582</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.3820741227775743</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.183048540124158</v>
+        <v>-1.183048540028014</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>54.67810206496629</v>
+        <v>54.67810206222514</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>37.75453483422483</v>
+        <v>37.75453484699413</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.7857190156112829</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-6.176283630135124</v>
+        <v>-6.176283630183171</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>54.92194317442267</v>
+        <v>54.92194303358973</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>35.1029317777166</v>
+        <v>35.10293177771661</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.9567766258121844</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0958878190139032</v>
+        <v>0.0958878192061835</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>56.53207817580785</v>
+        <v>56.53207818867043</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>25.56686262549697</v>
+        <v>25.56686271197566</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.6293160744192784</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>1.146203546143385</v>
+        <v>1.146203546083294</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>496.6894975653068</v>
+        <v>496.6894975653069</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>1195</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45.1647860360041</v>
+        <v>45.16478603228927</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15.34007685143156</v>
+        <v>15.3400768836689</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.6169973544641724</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>4.977192496395062</v>
+        <v>4.977192495673904</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>490.5561638857645</v>
+        <v>490.556163885765</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>87.7</v>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.27043194283701</v>
+        <v>54.27043196744194</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>25.42311787074285</v>
+        <v>25.42311788262887</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.5829207772436857</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0393786941462823</v>
+        <v>0.0393786939540063</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>486.5628000316162</v>
+        <v>486.5628000316183</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>115.5</v>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>57.79831896721706</v>
+        <v>57.79831864149693</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18.79603346803991</v>
+        <v>18.79603350054156</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>0.3880258780331017</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.484835822651646</v>
+        <v>0.4848358238533723</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>473.33627582486</v>
+        <v>473.3362758248573</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>24.1</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>56.67365361416208</v>
+        <v>56.67365356137509</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>19.9889933015307</v>
+        <v>19.98899331611396</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.6706224607875299</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0498264658311689</v>
+        <v>0.0498264658672204</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>472.9037658122512</v>
+        <v>472.9037658122501</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>5575</v>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.04528800116154</v>
+        <v>52.04528798519506</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11.69305823744509</v>
+        <v>11.69305830808589</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.5728205667649403</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>31.46568161468948</v>
+        <v>31.46568161829496</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>468.0328157905217</v>
+        <v>468.0328157905218</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>421</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>49.67736785338496</v>
+        <v>49.67736786122421</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>28.835958292447</v>
+        <v>28.83595829267376</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.6471612400226758</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0550277861415358</v>
+        <v>-0.0550277873432746</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.87352637436982</v>
+        <v>50.87352638483091</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>17.92504452498463</v>
+        <v>17.92504458256967</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>1.163762772921273</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.3501849271105745</v>
+        <v>0.3501849270504911</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.1032947298192</v>
+        <v>50.10329477465732</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21.55546829569838</v>
+        <v>21.55546833489858</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.4259700814411203</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1056811239041529</v>
+        <v>0.1056811238801204</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>448.5378324189813</v>
+        <v>448.5378324189812</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>100.5</v>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>48.32285828637959</v>
+        <v>48.32285850939702</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20.040948937815</v>
+        <v>20.0409489217368</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.3640116687412575</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.1629282914240892</v>
+        <v>0.1629282895013101</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>51.00808673813849</v>
+        <v>51.00808682562293</v>
       </c>
       <c r="I63" s="2" t="n">
         <v>29.57421617637868</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.8889113862040228</v>
+        <v>0.8889113857233217</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>42.38974280327943</v>
+        <v>42.38974276410438</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>16.7359633916341</v>
+        <v>16.73596341283164</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.1674061600921483</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.3328560194458895</v>
+        <v>-0.3328560194699223</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>439.4613797171348</v>
+        <v>439.4613797171333</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>39.5</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>54.70594203827836</v>
+        <v>54.70594195388935</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>24.35656301897063</v>
+        <v>24.35656326934681</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>2.407765344398479</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.2280600990058658</v>
+        <v>0.2280600992101636</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.84522978981229</v>
+        <v>47.84522980760068</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>7.540572312280814</v>
+        <v>7.540572314720303</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.5769033129826593</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.8792172338603175</v>
+        <v>0.8792172326586023</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45.0849308053389</v>
+        <v>45.08493081167318</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16.63049652299429</v>
+        <v>16.63049660300517</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.4978613986623879</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.2562077696609277</v>
+        <v>0.2562077696489016</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>407.9725395491897</v>
+        <v>407.9725395491898</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>103.5</v>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46.61624856703296</v>
+        <v>46.61624858052419</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>32.72428098669584</v>
+        <v>32.72428100571619</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>1.690507786029236</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.604376876693282</v>
+        <v>0.6043768766211819</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.93485825291294</v>
+        <v>51.93485826412152</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>3.521058822162868</v>
+        <v>3.52105891112504</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>1.140350288776941</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0643474599042566</v>
+        <v>0.0643474598922385</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>47.84633261046508</v>
+        <v>47.84633247749867</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>27.87336314441082</v>
+        <v>27.87336329965351</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.7365897181654893</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.3077326702286176</v>
+        <v>0.3077326707093224</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>400.3228159019485</v>
+        <v>400.3228159019436</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>27</v>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.96708635200682</v>
+        <v>50.96708633877626</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>28.9935678727525</v>
+        <v>28.99356786898994</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.3424332478416957</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.134839972081054</v>
+        <v>0.134839972117105</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>42.22283952548904</v>
+        <v>42.22283951459619</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>23.78749696023577</v>
+        <v>23.78749700255358</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.9376283161202454</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-8.477996267734937</v>
+        <v>-8.477996268816465</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>386.5852268132572</v>
+        <v>386.5852268132571</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>18</v>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>55.29037478876737</v>
+        <v>55.29037482554875</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>14.52618586262748</v>
+        <v>14.52618580699394</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>2.70414668793422</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.8087945813965822</v>
+        <v>0.8087945811322008</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>382.0103818425441</v>
+        <v>382.0103818425447</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>43.2</v>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.18083497098547</v>
+        <v>45.18083497580241</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15.417570663253</v>
+        <v>15.41757064844356</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>1.088988554589016</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.2400524017806486</v>
+        <v>0.2400524016003936</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>42.30951235131371</v>
+        <v>42.30951237502908</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.91767579666506</v>
+        <v>13.91767587455112</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.7527343987928723</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.6734510059318398</v>
+        <v>-0.6734510062923745</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>44.12994973743514</v>
+        <v>44.12994948286578</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.05400858504866</v>
+        <v>20.05400860442172</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>2.921391987367654</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0208119116676522</v>
+        <v>-0.0208119113311681</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>358.4760665744067</v>
+        <v>358.4760665744066</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>78.90000000000001</v>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>52.67415913903354</v>
+        <v>52.67415914763877</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>16.76882189620423</v>
+        <v>16.76882190490386</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.6159773522481475</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.5296212085930062</v>
+        <v>0.5296212084488022</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>44.78915607188766</v>
+        <v>44.78915594431876</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>14.37777899772824</v>
+        <v>14.37777906156054</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.2960801209436421</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.1373280435295672</v>
+        <v>-0.1373280434334248</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.57313431378976</v>
+        <v>51.5731342558962</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.10069650631083</v>
+        <v>18.10069645620608</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.8006348097026877</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.7544665883053154</v>
+        <v>0.7544665881851427</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>38.38011919470132</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.31500520721642</v>
+        <v>19.31500566654826</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>1.835561939772701</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0242238456906397</v>
+        <v>0.0242238457507254</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>52.60938929429401</v>
+        <v>52.6093892832286</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>16.62940385459855</v>
+        <v>16.62940393602072</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.4874922537721792</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>2.126052321378357</v>
+        <v>2.126052321162021</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>40.74956787591968</v>
+        <v>40.74956787711988</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>15.30262190307135</v>
+        <v>15.30262193866628</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-1.827411258314468</v>
+        <v>-1.827411258146226</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>47.47659813469829</v>
+        <v>47.47659796923825</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.00981422852612</v>
+        <v>15.00981420792055</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.8604789287030653</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.1101373656368981</v>
+        <v>0.1101373657090015</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>323.5126855444195</v>
+        <v>323.5126855444196</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>34.3</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>49.66622949997304</v>
+        <v>49.66622880371294</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>31.5832025205298</v>
+        <v>31.58320256157418</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.6850230461123523</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.145748121689812</v>
+        <v>-0.1457481210168421</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>48.77258409237539</v>
+        <v>48.77258351304166</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>14.02569976876042</v>
+        <v>14.02569956253096</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.9922289282288724</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0238215498603316</v>
+        <v>0.0238215499564229</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>41.64580686829242</v>
+        <v>41.64580683957967</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>9.406252666683258</v>
+        <v>9.406252627375869</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>1.185098328064244</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1797636419483321</v>
+        <v>0.1797636418865478</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>318.7914421473522</v>
+        <v>318.7914421473526</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>62.5</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>41.61559882823463</v>
+        <v>41.61559746803179</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>24.89577662866258</v>
+        <v>24.89577718367942</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>1.205240586704962</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.325304199880271</v>
+        <v>0.3253042019232228</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>317.339954911232</v>
+        <v>317.3399549112315</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>168</v>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46.34067468086418</v>
+        <v>46.34067470833464</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>13.64863592572729</v>
+        <v>13.64863608443968</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.8816950788172239</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.1069853220640617</v>
+        <v>-0.106985322280404</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>44.55516494287926</v>
+        <v>44.55516487384117</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>7.741277903514341</v>
+        <v>7.741277907761123</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>1.061630723977469</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.10006100095028</v>
+        <v>41.10006108390709</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.25526461937799</v>
+        <v>14.25526465804545</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>1.523325087508403</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.09937463424993841</v>
+        <v>0.099374634273968</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>299.9093986416535</v>
+        <v>299.9093986416524</v>
       </c>
       <c r="E91" s="2" t="n">
         <v>36.1</v>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>33.25295697484269</v>
+        <v>33.25295701424386</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16.40203552758541</v>
+        <v>16.40203578324442</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>1.636353862264569</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.2409906207560992</v>
+        <v>-0.2409906211406553</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>48.77287710712907</v>
+        <v>48.77287693644514</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.51442681894661</v>
+        <v>12.51442687779584</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.4348668324621864</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.2541926796307566</v>
+        <v>-0.2541926800426635</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>291.317210347153</v>
+        <v>291.3172103471529</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>59.9</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>46.17215873510872</v>
+        <v>46.17215950310087</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>9.216922855944976</v>
+        <v>9.216922880374089</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>1.249264594028412</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.09504237893361581</v>
+        <v>0.0950423781885453</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>45.11486981408318</v>
+        <v>45.11486982112562</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>14.47422050402955</v>
+        <v>14.47422045229279</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.3811414374332916</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.2262497860322402</v>
+        <v>0.2262497860442558</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>41.76788306841641</v>
+        <v>41.76788383077785</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>25.9540047359469</v>
+        <v>25.95400442126441</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.2089990252039252</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0533109120463983</v>
+        <v>0.0533109114936002</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>51.488743295798</v>
+        <v>51.48874331515211</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>7.413113537644509</v>
+        <v>7.413113448963617</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.0616895534910118</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.2830577764091596</v>
+        <v>0.2830577763731065</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>274.1807817869298</v>
+        <v>274.1807817869297</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>25.8</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>48.05776732579494</v>
+        <v>48.05776733780432</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>20.95541984737102</v>
+        <v>20.95541979695023</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.4051523792768494</v>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45.07401217972424</v>
+        <v>45.07401198473636</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12.06075918347341</v>
+        <v>12.06075913841485</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.6677909634672433</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1392495284820216</v>
+        <v>-0.1392495279532573</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>41.69041987627492</v>
+        <v>41.69041962069908</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>16.73243016912364</v>
+        <v>16.73243041459309</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.4163025262967711</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0685617920240111</v>
+        <v>0.0685617919278729</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>255.0471086599354</v>
+        <v>255.0471086599353</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>93.3</v>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>36.11295329110976</v>
+        <v>36.11295278503218</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>9.798471226473838</v>
+        <v>9.798471254467136</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>2.487407043997548</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.1935775210738975</v>
+        <v>-0.193577520112533</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>44.62086216214763</v>
+        <v>44.62086219667224</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>22.76719014609892</v>
+        <v>22.76719004007565</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.0758739211042115</v>
@@ -5838,7 +5838,7 @@
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>238.3841345843215</v>
+        <v>238.3841345843227</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>22.3</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>40.93586023042185</v>
+        <v>40.93586028822313</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17.03011852028452</v>
+        <v>17.03011854407021</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.9075224382208136</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0419286807018686</v>
+        <v>-0.0419286807138878</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>231.0569135764281</v>
+        <v>231.056913576428</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>44.15</v>
@@ -5908,7 +5908,7 @@
         <v>43.2078597571998</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>26.98343145902366</v>
+        <v>26.98343172648024</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.5685829799822503</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0166069864173007</v>
+        <v>-0.0166069864894063</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>230.3960435151252</v>
+        <v>230.3960435151257</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>51</v>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>47.00197673440443</v>
+        <v>47.00197664977547</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>10.07706021861419</v>
+        <v>10.07706028723438</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>1.38745756334259</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0002543061124941</v>
+        <v>-0.0002543060884649</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>228.8653854294278</v>
+        <v>228.8653854294277</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>868</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>37.84148844451587</v>
+        <v>37.84148837808175</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.41429763359527</v>
+        <v>13.41429769405833</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.8474657377354361</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>2.889963616940307</v>
+        <v>2.889963613335127</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>227.5962448273092</v>
+        <v>227.596244827311</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>34.65</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46.662072382813</v>
+        <v>46.66207208234515</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>24.80677598090175</v>
+        <v>24.80677599942341</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.6476808746442609</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0082952622779786</v>
+        <v>-0.008295261809307</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.47012988963206</v>
+        <v>46.47012986403792</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9.076027381227568</v>
+        <v>9.076027414832756</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.3064093180084713</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0370086347024067</v>
+        <v>0.0370086347144194</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>208.4147303012684</v>
+        <v>208.4147303012683</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>45.95</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>43.44224238305644</v>
+        <v>43.44224236614954</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.80225797012829</v>
+        <v>12.80225798746838</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.354691712174793</v>
@@ -6209,7 +6209,7 @@
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>192.4196536978067</v>
+        <v>192.4196536978065</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>73</v>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>32.07702986363576</v>
+        <v>32.07702994424456</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.34389015746456</v>
+        <v>18.34388997749882</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>1.450007571509841</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.130055043177476</v>
+        <v>0.1300550426967679</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>42.35688527511441</v>
+        <v>42.35688529633865</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>10.2330487939857</v>
+        <v>10.233048762671</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.958165478506654</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0012777892768378</v>
+        <v>0.0012777891326254</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.52613751987526</v>
+        <v>50.52613753742693</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>16.30507301775355</v>
+        <v>16.30507279431471</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.2102735870154775</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0595770887652129</v>
+        <v>0.0595770885008314</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>148.605901010752</v>
+        <v>148.6059010107519</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>42.75</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>48.96324100123464</v>
+        <v>48.96324073018989</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.23222113048167</v>
+        <v>19.23222110587582</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.7730287448142529</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0069697375357186</v>
+        <v>0.0069697374876498</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>47.91922590086912</v>
+        <v>47.91922551134112</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>8.780249822181149</v>
+        <v>8.780249705362722</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.963897398420272</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0452194382076676</v>
+        <v>0.0452194386643302</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45.78275577003692</v>
+        <v>45.7827557655602</v>
       </c>
       <c r="I114" s="2" t="n">
         <v>18.70922704152799</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.2373580357377152</v>
+        <v>-0.2373580357016701</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.7037802253525</v>
+        <v>44.70378022383345</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8.288036179015641</v>
+        <v>8.288036290790041</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.0008963585434173</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.6926433050163903</v>
+        <v>-0.692643304968322</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
